--- a/data/Clearance_rate_estimation_tool_TNC.xlsx
+++ b/data/Clearance_rate_estimation_tool_TNC.xlsx
@@ -192,7 +192,7 @@
     <t>CR = 7.38 * exp( -0.00246 * (T - 18.5)^2 ) * W</t>
   </si>
   <si>
-    <t>Using an allometric relationship of 1, which is based on wwet weight</t>
+    <t>Using an allometric relationship of 1, which is based on wet weight</t>
   </si>
   <si>
     <t>CR = 7.475 * exp( -0.00473 * (T - 29.1)^2 ) * W^(0.75)</t>
@@ -571,7 +571,7 @@
     <t>Important caveats</t>
   </si>
   <si>
-    <t xml:space="preserve"> There are a number of caveats as to how the "volume of water cleared" should be interpreted. Please be mindful of the fact that these estimates are a best case scenario derived only on water temperature and bivalve size alone and do not account for: particle size, salinity, particulate matter concentration, water flow rate, pollutant concentrations, diurnal variability; all of which may negatively affect the clearance rate. Furthmore, this tool does not account for re-fitration of water, and assumes a perfectly mixed watercolumn.</t>
+    <t xml:space="preserve"> There are a number of caveats as to how the "volume of water cleared" should be interpreted. Please be mindful of the fact that these estimates are a best case scenario derived only on water temperature and bivalve size alone and do not account for: particle size, salinity, particulate matter concentration, water flow rate, pollutant concentrations, diurnal variability; all of which may negatively affect the clearance rate. Furthermore, this tool does not account for re-filtration of water, and assumes a perfectly mixed water column.</t>
   </si>
   <si>
     <t>This tool is designed to allow growers to estimate the potential maximum volume of water cleared by the bivalves being grown on site.</t>
@@ -586,7 +586,7 @@
     <t>Enter your mean shell height into the yellow cell. The form will automatically fill in an estimated dry tissue weight for the inputted shell height.</t>
   </si>
   <si>
-    <t>Enter your water temperature into the green cell. The estiamted volume of water cleared will be automatically generated.</t>
+    <t>Enter your water temperature into the green cell. The estimated volume of water cleared will be automatically generated.</t>
   </si>
   <si>
     <t>To account for different size classes of bivalves, these can be entered independently (size and number of individuals), and the totals summed.</t>

--- a/data/Clearance_rate_estimation_tool_TNC.xlsx
+++ b/data/Clearance_rate_estimation_tool_TNC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pzuermg/Documents/Free_Lance_Projects/TNC_filtration_model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F69A4930-958F-E74F-B6EA-A10DCA614F0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAF0CA74-1EAB-2247-B469-062DD362AAEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="140" yWindow="920" windowWidth="30240" windowHeight="13500" activeTab="1" xr2:uid="{4524DFD7-3AE3-A24A-B6DE-70A1E37A7C23}"/>
+    <workbookView xWindow="1860" yWindow="3180" windowWidth="29820" windowHeight="13240" activeTab="3" xr2:uid="{4524DFD7-3AE3-A24A-B6DE-70A1E37A7C23}"/>
   </bookViews>
   <sheets>
     <sheet name="How to use" sheetId="21" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="137">
   <si>
     <t>Species</t>
   </si>
@@ -78,9 +78,6 @@
     <t>Yoon Kang et al. 2006</t>
   </si>
   <si>
-    <t>Ibarrola et al. 2026</t>
-  </si>
-  <si>
     <t>CR=(4.825-(0.013*(Temp-18.954)^2))*W^0.439</t>
   </si>
   <si>
@@ -141,9 +138,6 @@
     <t>Clearance_rate_formula</t>
   </si>
   <si>
-    <t>Length-weight conversion(mm to g dry tissue weight)</t>
-  </si>
-  <si>
     <t>Location</t>
   </si>
   <si>
@@ -183,18 +177,9 @@
     <t>NB: please select or input data in columns indicated in bold.</t>
   </si>
   <si>
-    <t>Equation as given in the reference</t>
-  </si>
-  <si>
     <t>O. edulis used as proxy: CR=(0.162+(0.072*1.131^Temp))*DW^0.622</t>
   </si>
   <si>
-    <t>CR = 7.38 * exp( -0.00246 * (T - 18.5)^2 ) * W</t>
-  </si>
-  <si>
-    <t>Using an allometric relationship of 1, which is based on wet weight</t>
-  </si>
-  <si>
     <t>CR = 7.475 * exp( -0.00473 * (T - 29.1)^2 ) * W^(0.75)</t>
   </si>
   <si>
@@ -450,33 +435,6 @@
   </si>
   <si>
     <r>
-      <t>Ibarrola, I., Pérez-Cebrecos, M., Antolín, C., Prieto, D., Urrutxurtu, I., Urrutia, M. B., ... &amp; Navarro, E. (2026). Energetic scaling mechanisms underlying family growth variation in Ruditapes decussatus. </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="13"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Marine Environmental Research</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>, 108237.</t>
-    </r>
-  </si>
-  <si>
-    <t>10.1016/j.marenvres.2026.108237</t>
-  </si>
-  <si>
-    <r>
       <t>Kang, H. Y., Lee, Y. J., Choi, K. S., Park, H. J., Yun, S. G., &amp; Kang, C. K. (2016). Combined effects of temperature and seston concentration on the physiological energetics of the Manila clam Ruditapes philippinarum. </t>
     </r>
     <r>
@@ -571,7 +529,7 @@
     <t>Important caveats</t>
   </si>
   <si>
-    <t xml:space="preserve"> There are a number of caveats as to how the "volume of water cleared" should be interpreted. Please be mindful of the fact that these estimates are a best case scenario derived only on water temperature and bivalve size alone and do not account for: particle size, salinity, particulate matter concentration, water flow rate, pollutant concentrations, diurnal variability; all of which may negatively affect the clearance rate. Furthermore, this tool does not account for re-filtration of water, and assumes a perfectly mixed water column.</t>
+    <t xml:space="preserve"> There are a number of caveats as to how the "volume of water cleared" should be interpreted. Please be mindful of the fact that these estimates are a best case scenario derived only on water temperature and bivalve size alone and do not account for: particle size, salinity, particulate matter concentration, water flow rate, pollutant concentrations, diurnal variability; all of which may negatively affect the clearance rate. Furthmore, this tool does not account for re-fitration of water, and assumes a perfectly mixed watercolumn.</t>
   </si>
   <si>
     <t>This tool is designed to allow growers to estimate the potential maximum volume of water cleared by the bivalves being grown on site.</t>
@@ -586,7 +544,7 @@
     <t>Enter your mean shell height into the yellow cell. The form will automatically fill in an estimated dry tissue weight for the inputted shell height.</t>
   </si>
   <si>
-    <t>Enter your water temperature into the green cell. The estimated volume of water cleared will be automatically generated.</t>
+    <t>Enter your water temperature into the green cell. The estiamted volume of water cleared will be automatically generated.</t>
   </si>
   <si>
     <t>To account for different size classes of bivalves, these can be entered independently (size and number of individuals), and the totals summed.</t>
@@ -653,9 +611,6 @@
     <t>Aracruz, ES, Brazil</t>
   </si>
   <si>
-    <t> Crassostrea rhizophorae</t>
-  </si>
-  <si>
     <t>Madrigal et al. 1985</t>
   </si>
   <si>
@@ -671,17 +626,554 @@
     <t>https://repositorio.una.ac.cr/server/api/core/bitstreams/02f6de5d-8386-4396-8593-9ed6d8d50b9d/content</t>
   </si>
   <si>
-    <t>CR may become available</t>
-  </si>
-  <si>
-    <t>CR = 0.000075 * (T + 11.65) * (L/mm)^2   l per hr</t>
+    <t>Pinna rudis</t>
+  </si>
+  <si>
+    <t>DW(g)=(length(mm))^2.5894*2.8291*10^-6</t>
+  </si>
+  <si>
+    <r>
+      <t>Riisgård, H. U., Larsen, P. S., &amp; Pleissner, D. (2014). Allometric equations for maximum filtration rate in blue mussels Mytilus edulis and importance of condition index. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Helgoland Marine Research</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>68</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(1), 193-198.</t>
+    </r>
+  </si>
+  <si>
+    <t>Riisgård et al. 2014</t>
+  </si>
+  <si>
+    <r>
+      <t>Kittner, C., &amp; Riisgård, H. U. (2005). Effect of temperature on filtration rate in the mussel Mytilus edulis: no evidence for temperature compensation. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Marine Ecology Progress Series</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>305</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, 147-152.</t>
+    </r>
+  </si>
+  <si>
+    <t>Kittner and Riisgård 2005</t>
+  </si>
+  <si>
+    <r>
+      <t>Schulte, E. H. (1975). Influence of algal concentration and temperature on the filtration rate of Mytilus edulis. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Marine biology</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(4), 331-341.</t>
+    </r>
+  </si>
+  <si>
+    <t>Schulte 1975</t>
+  </si>
+  <si>
+    <t>Kittner and Riisgård 2005, Riisgård et al. 2014, Schulte 1975</t>
+  </si>
+  <si>
+    <t>DTW(g)=0.000027*Length(mm)^2.525</t>
+  </si>
+  <si>
+    <r>
+      <t>Ibarrola, I., Arambalza, U., Navarro, J. M., Urrutia, M. B., &amp; Navarro, E. (2012). Allometric relationships in feeding and digestion in the Chilean mytilids Mytilus chilensis (Hupé), Choromytilus chorus (Molina) and Aulacomya ater (Molina): a comparative study. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Journal of Experimental Marine Biology and Ecology</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>426</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, 18-27.</t>
+    </r>
+  </si>
+  <si>
+    <t>Ibarrola et al. 2012</t>
+  </si>
+  <si>
+    <t>Corral bay (Chile)</t>
+  </si>
+  <si>
+    <t>January (summer)</t>
+  </si>
+  <si>
+    <r>
+      <t>Navarro, J. M., &amp; Winter, J. E. (1982). Ingestion rate, assimilation efficiency and energy balance in Mytilus chilensis in relation to body size and different algal concentrations. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Marine Biology</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>67</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(3), 255-266.</t>
+    </r>
+  </si>
+  <si>
+    <t>Navarro &amp; Winter 1982</t>
+  </si>
+  <si>
+    <t>Yaldad Bay (southern Chile)</t>
+  </si>
+  <si>
+    <t>February (summer)</t>
+  </si>
+  <si>
+    <t>DTW(g)=0.0089*L(cm)^2.82</t>
+  </si>
+  <si>
+    <t>Only valid for water temperatures between 10-14C</t>
+  </si>
+  <si>
+    <t>CR (l/h) = 2.454 * (W / g)^0.492</t>
+  </si>
+  <si>
+    <t>Lopez Bascur 2013</t>
+  </si>
+  <si>
+    <r>
+      <t>Lopez Bascur, J. A.(2013). </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Respuesta fisiologica de </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mytilus chilensis (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>chorito) en cultivo suspendido (dalcahue, chiloe) y su relacion con las variables ambientales (Doctoral Dissertation, Universidad Austral</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> De Chile).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Sarà, G., &amp; Mazzola, A. (1997). Effects of trophic and environmental conditions on the growth of Crassostrea gigas in culture. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Aquaculture</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>153</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(1-2), 81-91.</t>
+    </r>
+  </si>
+  <si>
+    <t>Sarà &amp; Mazzola 1997</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>Equation as given in the reference.</t>
+  </si>
+  <si>
+    <t>DTW(g)=0.0041*L(cm)^2.54</t>
+  </si>
+  <si>
+    <t>Marlborough Sounds, New Zealand</t>
+  </si>
+  <si>
+    <t>April (Autumn)</t>
+  </si>
+  <si>
+    <t>CR =   l per hr (0.0000513 * T + 0.000599) * (L in mm)^2.088 / (1 + exp(-2(T-4.1)) + exp(2(T-25)))</t>
+  </si>
+  <si>
+    <t>CR = 4.16 exp( -0.0181 (T - 14.88)^2 ) * W^0.58</t>
+  </si>
+  <si>
+    <t>Sobral and Widdows 1997</t>
+  </si>
+  <si>
+    <r>
+      <t>Sobral, P. &amp; Widdows, J. (1997). Effects of elevated temperatures on the scope for growth and resistance to air exposure of the clam Ruditapes decussatus (L.), from southern Portugal. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Scientia Marina</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>. 61:163-171</t>
+    </r>
+  </si>
+  <si>
+    <t>Filgueria et al. 2008, Arranz et al. 2016</t>
+  </si>
+  <si>
+    <r>
+      <t>Arranz, K., Labarta, U., Fernández-Reiriz, M. J., &amp; Navarro, E. (2016). Allometric size-scaling of biometric growth parameters and metabolic and excretion rates. A comparative study of intertidal and subtidal populations of mussels (Mytilus galloprovincialis). </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hydrobiologia</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>772</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(1), 261-275.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Filgueira, R., Labarta, U., &amp; Fernández-Reiriz, M. J. (2008). Effect of condition index on allometric relationships of clearance rate in Mytilus galloprovincialis Lamarck, 1819. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Revista de biología marina y oceanografía</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>43</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(2), 391-398.</t>
+    </r>
+  </si>
+  <si>
+    <t>Filgueria et al. 2008</t>
+  </si>
+  <si>
+    <t>Arranz et al. 2016</t>
+  </si>
+  <si>
+    <t>https://dialnet.unirioja.es/descarga/articulo/5295154.pdf</t>
+  </si>
+  <si>
+    <t>https://idp.springer.com/authorize/casa?redirect_uri=https://link.springer.com/content/pdf/10.1007/s10750-016-2672-3.pdf&amp;casa_token=z8bEXwsk2owAAAAA:dI1bb2qz59PAC7lgcTIdXTKZzrCP5FMeg1x29dR4HFpHjmHtDx5ULGT0n02Oi9PR4I8soCSRHqF62szTZg</t>
+  </si>
+  <si>
+    <t>https://www.researchgate.net/publication/239558985_Effects_of_elevated_temperatures_on_the_scope_for_growth_and_resistance_to_air_exposure_of_the_clam_Ruditapes_decussatus_L_from_southern_Portugal</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S0044848697000094</t>
+  </si>
+  <si>
+    <t>http://cybertesis.uach.cl/tesis/uach/2013/fcl864r/doc/fcl864r.pdf</t>
+  </si>
+  <si>
+    <t>https://link.springer.com/article/10.1007/BF00397666</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/abs/pii/S0022098112001773</t>
+  </si>
+  <si>
+    <t>https://link.springer.com/article/10.1007/BF00390638</t>
+  </si>
+  <si>
+    <t>Not required</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">NB this data is for the proxy specues </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ostrea edulis</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">CR = 5.14 * exp( -0.00246 * (T - 18.5)^2 ) (W in g)^0.7 l per hour </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -754,6 +1246,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="14"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -803,7 +1314,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -818,8 +1329,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1160,47 +1672,47 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1228,19 +1740,19 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" t="s">
         <v>15</v>
-      </c>
-      <c r="F1" t="s">
-        <v>16</v>
       </c>
       <c r="G1" t="s">
         <v>3</v>
@@ -1249,43 +1761,44 @@
         <v>4</v>
       </c>
       <c r="I1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B2" t="str">
         <f>VLOOKUP(A2,Final_equations!A:C,3,FALSE)</f>
-        <v>CR = 0.000075 * (T + 11.65) * (L/mm)^2   l per hr</v>
+        <v>CR=(4.825-(0.013*(Temp-18.954)^2))*W^0.439</v>
       </c>
       <c r="C2" s="8">
         <v>50</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <f>VLOOKUP(Filtration_calculator!A2,'length-weight_conversions'!A1:E16,5,FALSE)</f>
+        <v>0.22193687543402596</v>
       </c>
       <c r="E2" s="9">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F2">
         <f>VLOOKUP(A2,Final_equations!A:B,2,FALSE)</f>
-        <v>7.8093749999999993</v>
+        <v>2.2462788857324916</v>
       </c>
       <c r="G2">
         <v>10000</v>
       </c>
       <c r="H2">
         <f>F2*G2</f>
-        <v>78093.75</v>
+        <v>22462.788857324915</v>
       </c>
       <c r="I2">
         <f>H2/1000*24</f>
-        <v>1874.25</v>
+        <v>539.10693257579794</v>
       </c>
     </row>
   </sheetData>
@@ -1308,52 +1821,177 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{060AC66F-7193-E948-864C-69260C6BDA23}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="45.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G1" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>89</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E2">
         <f>-0.451+0.0186*Filtration_calculator!C2</f>
         <v>0.47899999999999993</v>
       </c>
       <c r="F2" t="s">
-        <v>85</v>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E4">
+        <f>0.000027*Filtration_calculator!C2^2.525</f>
+        <v>0.52633593876385154</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" t="s">
+        <v>104</v>
+      </c>
+      <c r="D5" t="s">
+        <v>105</v>
+      </c>
+      <c r="E5">
+        <f>0.0089*(Filtration_calculator!C2/10)^2.82</f>
+        <v>0.83269396840975929</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="C6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E6">
+        <f>0.0041*(Filtration_calculator!C2/10)^2.48</f>
+        <v>0.22193687543402596</v>
+      </c>
+      <c r="F6" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G14" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -1364,7 +2002,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21EFCE0E-BF21-284D-9260-958A019E1EE9}">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.83203125" bestFit="1" customWidth="1"/>
@@ -1374,15 +2012,15 @@
     <col min="6" max="6" width="43.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>1</v>
@@ -1390,207 +2028,213 @@
       <c r="E1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" s="4" t="s">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="B2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="B3">
         <f>(4.825-(0.013*(Filtration_calculator!E2-18.954)^2))*Filtration_calculator!D2^0.439</f>
-        <v>3.2388164920000007</v>
+        <v>2.2462788857324916</v>
       </c>
       <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
       <c r="E3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B4">
         <f>16.34*EXP(-0.0152*(Filtration_calculator!E2-28.6)^2 )*Filtration_calculator!D2^0.608</f>
-        <v>15.860378633870544</v>
+        <v>5.3728786251102285</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B5">
         <f>7.475*EXP(-0.00473*(Filtration_calculator!E2-29.1)^2 )*Filtration_calculator!D2^(0.75)</f>
-        <v>7.4464158247405852</v>
+        <v>2.2322970162229376</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
         <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B6">
         <f>13.1*EXP(-0.0099*(Filtration_calculator!E2-28.3)^2)*Filtration_calculator!D2^0.617</f>
-        <v>12.730506888620562</v>
+        <v>4.6459352705033501</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7">
+        <f>4.16*EXP(-0.0181*(Filtration_calculator!E2-14.88)^2)*Filtration_calculator!D2^0.58</f>
+        <v>0.27217890510661769</v>
+      </c>
+      <c r="C7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D7" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
+      <c r="B8">
+        <f>5.14*EXP(-0.00246*(Filtration_calculator!E2- 18.5)^2 )*Filtration_calculator!D2^0.7</f>
+        <v>1.6150476837206291</v>
+      </c>
+      <c r="C8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="B8">
-        <f>7.38*EXP(-0.00246*(Filtration_calculator!E2- 18.5)^2 )*Filtration_calculator!D2</f>
-        <v>5.3304658646746583</v>
-      </c>
-      <c r="C8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>25</v>
       </c>
       <c r="B9">
         <f>2.54*EXP(-0.00411*(Filtration_calculator!E2-27.9)^2)*Filtration_calculator!D2^0.792</f>
-        <v>2.4943769561135478</v>
+        <v>0.74479374844388146</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
       </c>
       <c r="E9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="B10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
-        <v>27</v>
       </c>
       <c r="B11" s="2">
         <f>5.04*EXP(-0.0454*(Filtration_calculator!E2-29.3)^2)*Filtration_calculator!D2^0.764</f>
-        <v>4.9291180724547896</v>
+        <v>0.68926001307004026</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="E11" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B12">
         <f>(0.162+(0.072*1.131^Filtration_calculator!E2))*Filtration_calculator!D2^0.622</f>
-        <v>3.0540822778673467</v>
+        <v>0.67622034421048982</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B13" s="2">
-        <f>0.000075*(Filtration_calculator!E2+11.65)*Filtration_calculator!C2^2</f>
-        <v>7.8093749999999993</v>
+        <f>(0.0000513*Filtration_calculator!E2+0.000599)*(Filtration_calculator!C2)^2.088/(1+EXP(-2*(Filtration_calculator!E2-4.1))+EXP(2*(Filtration_calculator!E2-25)))</f>
+        <v>3.3183607362271923</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+        <v>117</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="6"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B14" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" t="s">
-        <v>95</v>
+      <c r="B15">
+        <f>2.454*(Filtration_calculator!D2)^0.492</f>
+        <v>1.1700905082900024</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
@@ -1600,7 +2244,7 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1611,7 +2255,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{264C9648-2F22-B347-91A2-7EAEF7624D43}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.33203125" bestFit="1" customWidth="1"/>
@@ -1619,22 +2263,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="C1" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C2" s="6" t="str">
         <f>HYPERLINK("http://dx.doi.org/10.1016/0044-8486(95)00036-2","http://dx.doi.org/10.1016/0044-8486(95)00036-2")</f>
@@ -1646,21 +2290,21 @@
         <v>9</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -1668,18 +2312,18 @@
         <v>7</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C6" s="6" t="str">
         <f>HYPERLINK("http://dx.doi.org/10.3354/meps170119","http://dx.doi.org/10.3354/meps170119")</f>
@@ -1691,7 +2335,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C7" s="6" t="str">
         <f>HYPERLINK("http://dx.doi.org/10.3354/meps195179","http://dx.doi.org/10.3354/meps195179")</f>
@@ -1699,66 +2343,166 @@
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
-        <v>11</v>
+      <c r="A8" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>69</v>
+        <v>63</v>
+      </c>
+      <c r="C8" s="6" t="str">
+        <f>HYPERLINK("http://dx.doi.org/10.1371/journal.pone.0152427","http://dx.doi.org/10.1371/journal.pone.0152427")</f>
+        <v>http://dx.doi.org/10.1371/journal.pone.0152427</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C9" s="6" t="str">
-        <f>HYPERLINK("http://dx.doi.org/10.1371/journal.pone.0152427","http://dx.doi.org/10.1371/journal.pone.0152427")</f>
-        <v>http://dx.doi.org/10.1371/journal.pone.0152427</v>
+        <f>HYPERLINK("http://dx.doi.org/10.1016/S0044-8486(98)00383-4","http://dx.doi.org/10.1016/S0044-8486(98)00383-4")</f>
+        <v>http://dx.doi.org/10.1016/S0044-8486(98)00383-4</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>14</v>
+        <v>78</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" s="6" t="str">
-        <f>HYPERLINK("http://dx.doi.org/10.1016/S0044-8486(98)00383-4","http://dx.doi.org/10.1016/S0044-8486(98)00383-4")</f>
-        <v>http://dx.doi.org/10.1016/S0044-8486(98)00383-4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C12" t="str">
+        <f>HYPERLINK("http://dx.doi.org/10.1007/s10152-013-0377-9","http://dx.doi.org/10.1007/s10152-013-0377-9")</f>
+        <v>http://dx.doi.org/10.1007/s10152-013-0377-9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A13" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C13" t="str">
+        <f>HYPERLINK("http://dx.doi.org/10.3354/meps305147","http://dx.doi.org/10.3354/meps305147")</f>
+        <v>http://dx.doi.org/10.3354/meps305147</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A14" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B14" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="C12" t="s">
-        <v>94</v>
+      <c r="C14" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A15" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="C15" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A16" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="C16" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A17" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C17" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>111</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="C18" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A19" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C19" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>125</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="C20" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>124</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C21" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C8" r:id="rId1" display="https://doi.org/10.1016/j.marenvres.2026.108237" xr:uid="{ECD2A9AD-0EA0-3F46-9065-046E426AA0A9}"/>
-    <hyperlink ref="C11" r:id="rId2" display="https://doi.org/10.2478/v10104-012-0024-0" xr:uid="{EAB88CC6-2AEF-6E43-8ADB-8A577117DB1E}"/>
+    <hyperlink ref="C10" r:id="rId1" display="https://doi.org/10.2478/v10104-012-0024-0" xr:uid="{EAB88CC6-2AEF-6E43-8ADB-8A577117DB1E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/data/Clearance_rate_estimation_tool_TNC.xlsx
+++ b/data/Clearance_rate_estimation_tool_TNC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pzuermg/Documents/Free_Lance_Projects/TNC_filtration_model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAF0CA74-1EAB-2247-B469-062DD362AAEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F4ABC1-6DD8-CA49-A545-9A1A478970C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1860" yWindow="3180" windowWidth="29820" windowHeight="13240" activeTab="3" xr2:uid="{4524DFD7-3AE3-A24A-B6DE-70A1E37A7C23}"/>
+    <workbookView xWindow="420" yWindow="3840" windowWidth="29820" windowHeight="13240" activeTab="3" xr2:uid="{4524DFD7-3AE3-A24A-B6DE-70A1E37A7C23}"/>
   </bookViews>
   <sheets>
     <sheet name="How to use" sheetId="21" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="187">
   <si>
     <t>Species</t>
   </si>
@@ -553,9 +553,6 @@
     <t>equation</t>
   </si>
   <si>
-    <t>(DW/g) = -0.451 + 0.0186 * (L/mm)</t>
-  </si>
-  <si>
     <r>
       <t>Sroczyńska, K., Barroso, G., &amp; Chícharo, L. (2012). In situ effective clearance rate measurement of mangrove oysters (Crassostrea rhizophorae) in a tropical estuary in Brazil. </t>
     </r>
@@ -614,9 +611,6 @@
     <t>Madrigal et al. 1985</t>
   </si>
   <si>
-    <t>For this species we have the potential to also build in salinity</t>
-  </si>
-  <si>
     <t>CR = 5.04 * exp( -0.0454 * (T - 29.3)^2 ) * DW^0.764</t>
   </si>
   <si>
@@ -626,12 +620,6 @@
     <t>https://repositorio.una.ac.cr/server/api/core/bitstreams/02f6de5d-8386-4396-8593-9ed6d8d50b9d/content</t>
   </si>
   <si>
-    <t>Pinna rudis</t>
-  </si>
-  <si>
-    <t>DW(g)=(length(mm))^2.5894*2.8291*10^-6</t>
-  </si>
-  <si>
     <r>
       <t>Riisgård, H. U., Larsen, P. S., &amp; Pleissner, D. (2014). Allometric equations for maximum filtration rate in blue mussels Mytilus edulis and importance of condition index. </t>
     </r>
@@ -1029,9 +1017,6 @@
     </r>
   </si>
   <si>
-    <t>Filgueria et al. 2008, Arranz et al. 2016</t>
-  </si>
-  <si>
     <r>
       <t>Arranz, K., Labarta, U., Fernández-Reiriz, M. J., &amp; Navarro, E. (2016). Allometric size-scaling of biometric growth parameters and metabolic and excretion rates. A comparative study of intertidal and subtidal populations of mussels (Mytilus galloprovincialis). </t>
     </r>
@@ -1151,8 +1136,65 @@
     <t>Not required</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">NB this data is for the proxy specues </t>
+    <t xml:space="preserve">CR = 5.14 * exp( -0.00246 * (T - 18.5)^2 ) (W in g)^0.7 l per hour </t>
+  </si>
+  <si>
+    <r>
+      <t>Cranford, P. J., Ward, J. E., &amp; Shumway, S. E. (2011). Bivalve filter feeding: variability and limits of the aquaculture biofilter. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Shellfish aquaculture and the environment</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, 81-124.</t>
+    </r>
+  </si>
+  <si>
+    <t>Cranford et al. 2011</t>
+  </si>
+  <si>
+    <t>http://nacsetac.org/wp-content/uploads/2021/05/Cranford_etal_2011_Shellf_Aq_Env-corrected.pdf</t>
+  </si>
+  <si>
+    <t>Filgueria et al. 2008, Arranz et al. 2016, Cranford et al. 2011</t>
+  </si>
+  <si>
+    <t>"Universal" allometric relationship used. Only valid for temps between 10 and 14C</t>
+  </si>
+  <si>
+    <t>Length-weight conversion is for Pinna rudis</t>
+  </si>
+  <si>
+    <t>Pinna nobilis</t>
+  </si>
+  <si>
+    <t>Vila Joiosa, Alicante (Spain) </t>
+  </si>
+  <si>
+    <t>unknown</t>
+  </si>
+  <si>
+    <t>DWmeat.mg = 0.00554 (H.mm)^2.69</t>
+  </si>
+  <si>
+    <t>Mar Menor, Spain</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">NB this data is for the proxy species </t>
     </r>
     <r>
       <rPr>
@@ -1164,16 +1206,296 @@
       </rPr>
       <t>Ostrea edulis</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">CR = 5.14 * exp( -0.00246 * (T - 18.5)^2 ) (W in g)^0.7 l per hour </t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. To obtain the height-weight conversion we fitted a linear model for log(Weight) as a function of log(height). The R^2 of the fit was 0.84.</t>
+    </r>
+  </si>
+  <si>
+    <t>Hernandes unpublished data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mundka, País vasco, Northern Spain </t>
+  </si>
+  <si>
+    <r>
+      <t>Urrutia, M. B., Ibarrola, I., Iglesias, J. I. P., &amp; Navarro, E. (1999). Energetics of growth and reproduction in a high-tidal population of the clam Ruditapes decussatus from Urdaibai Estuary (Basque Country, N. Spain). </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Journal of Sea Research</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>42</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(1), 35-48.</t>
+    </r>
+  </si>
+  <si>
+    <t>Urrutia et al. 1999</t>
+  </si>
+  <si>
+    <t>Summer</t>
+  </si>
+  <si>
+    <t>Autumn</t>
+  </si>
+  <si>
+    <t>Winter</t>
+  </si>
+  <si>
+    <t>Spring</t>
+  </si>
+  <si>
+    <t>Noted that this is for a natural intertidal population and condition may therefore be lower than in aquaculture. Length to weight shows strong seasonal variability. The values presented here are the mean values by season.</t>
+  </si>
+  <si>
+    <t>DTW (g)=  0.00000321 L(mm)^2.54</t>
+  </si>
+  <si>
+    <t>DTW(g)=1.703*10^-5*(Lmm)^2.891</t>
+  </si>
+  <si>
+    <t>DTW(g)=1.815*10^-5*(Lmm)^2.909</t>
+  </si>
+  <si>
+    <t>DTW(g)=1.610*10^-5*(Lmm)^2.906</t>
+  </si>
+  <si>
+    <t>DTW(g)=1.773*10^-5*(Lmm)^2.870</t>
+  </si>
+  <si>
+    <t>Fangar, Ebro Delta</t>
+  </si>
+  <si>
+    <t>Masnou, Ebro Delta</t>
+  </si>
+  <si>
+    <t>Annual</t>
+  </si>
+  <si>
+    <t>DTW(g)=(0.169*10^-5)*L(mm)^3.1475</t>
+  </si>
+  <si>
+    <t>DTW(g)=(0.137*10^-5)*L(mm)^3.2171</t>
+  </si>
+  <si>
+    <r>
+      <t>Ramón, M., Fernández, M., &amp; Galimany, E. (2007). Development of mussel (Mytilus galloprovincialis) seed from two different origins in a semi-enclosed Mediterranean Bay (NE Spain). </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Aquaculture</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>264</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(1-4), 148-159.</t>
+    </r>
+  </si>
+  <si>
+    <t>Ramón et al. 2007</t>
+  </si>
+  <si>
+    <t>DTW(g) = -0.451 + 0.0186 * (L/mm)</t>
+  </si>
+  <si>
+    <t>Alvarez Jorna, P. (1995) Crecimiento, reproducción y energética fisiológica de la almeja tapes philippinarum. PhD Thesis. Universidad del País Vasco - Euskal Herriko Unibertsitatea</t>
+  </si>
+  <si>
+    <t>Alvarez Jorna, P. (1995)</t>
+  </si>
+  <si>
+    <t>Cantabria (Northern Spain)</t>
+  </si>
+  <si>
+    <t>DTW(g)=18.9936333*10^-6*(Lmm)^2.7178</t>
+  </si>
+  <si>
+    <t>DTW(g)=12.39494*10^-6*(Lmm)^2.89704</t>
+  </si>
+  <si>
+    <t>DTW(g)=13.7052875*10^-6*(Lmm)^2.8253</t>
+  </si>
+  <si>
+    <t>DTW(g)=17.1689125*10^-6*(Lmm)^2.7503</t>
+  </si>
+  <si>
+    <t>Pinna rudis</t>
+  </si>
+  <si>
+    <t>Hernandes et al. 2021</t>
+  </si>
+  <si>
+    <r>
+      <t>Hernandis, S., Ibarrola, I., Tena-Medialdea, J., Albentosa, M., Prado, P., Vázquez-Luis, M., &amp; García-March, J. R. (2023). Physiological responses of the fan mussel Pinna nobilis to temperature: ecological and captivity implications. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mediterranean Marine Science</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Hernandis et al. 2023</t>
+  </si>
+  <si>
+    <t>Hernandes et al. 2023 and Hernandes unpublished data</t>
+  </si>
+  <si>
+    <t>CR(L/h)= 18.3 exp( -0.00889 * (T - 26.8)^2 ) * (DTW)^0.784</t>
+  </si>
+  <si>
+    <t>CR(L/h)= 12.3 exp( -0.00889 * (T - 26.8)^2 ) * (DTW)^0.784</t>
+  </si>
+  <si>
+    <r>
+      <t>Hernandis, S., Tena-Medialdea, J., Téllez, C., López, D., Prado, P., &amp; García-March, J. R. (2021). Suspended culture of Pinna rudis enhances survival and allows the development of a seasonal growth model for Mediterranean Pinnids. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Aquaculture</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>543</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, 736964.</t>
+    </r>
+  </si>
+  <si>
+    <t>https://repositori.irta.cat/bitstream/handle/20.500.12327/1454/Hernandis_Suspended_2021.pdf?sequence=1</t>
+  </si>
+  <si>
+    <t>https://repositori.irta.cat/bitstream/handle/20.500.12327/2228/Hernandis_Physiological_2023.pdf?sequence=1</t>
+  </si>
+  <si>
+    <t>https://ecowin.org/pdf/documents/Ramon%20et%20al%202007%20Gallo%20mussel%20seed%20Aquaculture.pdf</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S1385110199000179</t>
+  </si>
+  <si>
+    <t>At the moment, the spreadsheet picks up the first of the listed length to dry tissue weight conversion listed. If an alternative location/season is preferable, this currently has to be manually selected.</t>
+  </si>
+  <si>
+    <t>Normalised to the Pinna rudis data, with temperature dependence derived from Pinna nobilis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weight dependence fitted to CR data from Pinna rudis data and  temperature dependence fitted to CR estimates for Pinna nobilis. </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1260,9 +1582,16 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Helvetica"/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1314,7 +1643,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1332,6 +1661,8 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1667,7 +1998,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F16E48E-7BF1-2943-A195-E1F668C1711F}">
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
@@ -1705,14 +2036,19 @@
         <v>74</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -1769,36 +2105,36 @@
     </row>
     <row r="2" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>18</v>
+        <v>172</v>
       </c>
       <c r="B2" t="str">
         <f>VLOOKUP(A2,Final_equations!A:C,3,FALSE)</f>
-        <v>CR=(4.825-(0.013*(Temp-18.954)^2))*W^0.439</v>
+        <v>CR(L/h)= 12.3 exp( -0.00889 * (T - 26.8)^2 ) * (DTW)^0.784</v>
       </c>
       <c r="C2" s="8">
         <v>50</v>
       </c>
       <c r="D2">
-        <f>VLOOKUP(Filtration_calculator!A2,'length-weight_conversions'!A1:E16,5,FALSE)</f>
-        <v>0.22193687543402596</v>
+        <f>VLOOKUP(Filtration_calculator!A2,'length-weight_conversions'!A1:E24,5,FALSE)</f>
+        <v>6.6357320876920228E-2</v>
       </c>
       <c r="E2" s="9">
         <v>25</v>
       </c>
       <c r="F2">
         <f>VLOOKUP(A2,Final_equations!A:B,2,FALSE)</f>
-        <v>2.2462788857324916</v>
+        <v>1.4248092309525136</v>
       </c>
       <c r="G2">
         <v>10000</v>
       </c>
       <c r="H2">
         <f>F2*G2</f>
-        <v>22462.788857324915</v>
+        <v>14248.092309525135</v>
       </c>
       <c r="I2">
         <f>H2/1000*24</f>
-        <v>539.10693257579794</v>
+        <v>341.95421542860322</v>
       </c>
     </row>
   </sheetData>
@@ -1809,7 +2145,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3695E807-2BCC-8241-87F6-1806B3929A7D}">
           <x14:formula1>
-            <xm:f>Final_equations!$A$2:$A$15</xm:f>
+            <xm:f>Final_equations!$A$2:$A$17</xm:f>
           </x14:formula1>
           <xm:sqref>A2</xm:sqref>
         </x14:dataValidation>
@@ -1821,7 +2157,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{060AC66F-7193-E948-864C-69260C6BDA23}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.6640625" bestFit="1" customWidth="1"/>
@@ -1848,7 +2184,7 @@
         <v>1</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -1856,49 +2192,65 @@
         <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
-        <v>76</v>
+        <v>164</v>
       </c>
       <c r="E2">
         <f>-0.451+0.0186*Filtration_calculator!C2</f>
         <v>0.47899999999999993</v>
       </c>
       <c r="F2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>87</v>
+        <v>137</v>
+      </c>
+      <c r="B3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C3" t="s">
+        <v>139</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>152</v>
+      </c>
+      <c r="E3">
+        <f>0.00000321*Filtration_calculator!C2^2.54</f>
+        <v>6.6357320876920228E-2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>173</v>
+      </c>
+      <c r="G3" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
-        <v>29</v>
+      <c r="A4" t="s">
+        <v>172</v>
       </c>
       <c r="B4" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>152</v>
       </c>
       <c r="E4">
-        <f>0.000027*Filtration_calculator!C2^2.525</f>
-        <v>0.52633593876385154</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>98</v>
+        <f>0.00000321*Filtration_calculator!C2^2.54</f>
+        <v>6.6357320876920228E-2</v>
+      </c>
+      <c r="F4" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -1906,92 +2258,333 @@
         <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="E5">
+        <f>0.000027*Filtration_calculator!C2^2.525</f>
+        <v>0.52633593876385154</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E6">
         <f>0.0089*(Filtration_calculator!C2/10)^2.82</f>
         <v>0.83269396840975929</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+      <c r="F6" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="C6" t="s">
-        <v>116</v>
-      </c>
-      <c r="D6" t="s">
-        <v>114</v>
-      </c>
-      <c r="E6">
+      <c r="B7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D7" t="s">
+        <v>110</v>
+      </c>
+      <c r="E7">
         <f>0.0041*(Filtration_calculator!C2/10)^2.48</f>
         <v>0.22193687543402596</v>
       </c>
-      <c r="F6" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
-        <v>19</v>
+      <c r="F7" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>157</v>
+      </c>
+      <c r="C11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D11" t="s">
+        <v>161</v>
+      </c>
+      <c r="E11">
+        <f>(0.137*10^-5)*Filtration_calculator!C2^3.2171</f>
+        <v>0.40038423423195663</v>
+      </c>
+      <c r="F11" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>158</v>
+      </c>
+      <c r="C12" t="s">
+        <v>159</v>
+      </c>
+      <c r="D12" t="s">
+        <v>160</v>
+      </c>
+      <c r="E12">
+        <f>(0.169*10^-5)*Filtration_calculator!C2^3.1475</f>
+        <v>0.37617921276716043</v>
+      </c>
+      <c r="F12" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
+        <v>144</v>
+      </c>
+      <c r="C13" t="s">
+        <v>147</v>
+      </c>
+      <c r="D13" t="s">
+        <v>153</v>
+      </c>
+      <c r="E13">
+        <f>1.703*10^-5*Filtration_calculator!C2^2.891</f>
+        <v>1.3897507929243837</v>
+      </c>
+      <c r="F13" t="s">
+        <v>146</v>
+      </c>
+      <c r="G13" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
+      </c>
+      <c r="B14" t="s">
+        <v>144</v>
+      </c>
+      <c r="C14" t="s">
+        <v>148</v>
+      </c>
+      <c r="D14" t="s">
+        <v>154</v>
+      </c>
+      <c r="E14">
+        <f>1.815*10^-5*Filtration_calculator!C2^2.909</f>
+        <v>1.5892066437896442</v>
+      </c>
+      <c r="F14" t="s">
+        <v>146</v>
       </c>
       <c r="G14" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" t="s">
+        <v>144</v>
+      </c>
+      <c r="C15" t="s">
+        <v>149</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="E15">
+        <f>1.61*10^-5*Filtration_calculator!C2^2.906</f>
+        <v>1.3932617316781033</v>
+      </c>
+      <c r="F15" t="s">
+        <v>146</v>
+      </c>
+      <c r="G15" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" t="s">
+        <v>144</v>
+      </c>
+      <c r="C16" t="s">
+        <v>150</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="E16">
+        <f>1.773*10^-5*Filtration_calculator!C2^2.87</f>
+        <v>1.3327621427137633</v>
+      </c>
+      <c r="F16" t="s">
+        <v>146</v>
+      </c>
+      <c r="G16" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="C17" t="s">
+        <v>147</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E17">
+        <f>12.39494*10^-6*Filtration_calculator!C2^2.89704</f>
+        <v>1.0356869169985046</v>
+      </c>
+      <c r="F17" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="C18" t="s">
+        <v>148</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="E18">
+        <f>18.9936333*10^-6*Filtration_calculator!C2^2.7178</f>
+        <v>0.78717034907255012</v>
+      </c>
+      <c r="F18" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="C19" t="s">
+        <v>149</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="E19">
+        <f>13.7052875*10^-6*Filtration_calculator!C2^2.8253</f>
+        <v>0.86494422538912696</v>
+      </c>
+      <c r="F19" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="C20" t="s">
+        <v>150</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="E20">
+        <f>17.1689125*10^-6*Filtration_calculator!C2^2.7503</f>
+        <v>0.80801605513018993</v>
+      </c>
+      <c r="F20" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" t="s">
+        <v>141</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="E22">
+        <f>0.00000554*(Filtration_calculator!C2)^2.69</f>
+        <v>0.20593922610985879</v>
+      </c>
+      <c r="F22" t="s">
+        <v>143</v>
+      </c>
+      <c r="G22" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B15" t="s">
-        <v>134</v>
+      <c r="B23" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -2043,7 +2636,7 @@
       </c>
       <c r="B3">
         <f>(4.825-(0.013*(Filtration_calculator!E2-18.954)^2))*Filtration_calculator!D2^0.439</f>
-        <v>2.2462788857324916</v>
+        <v>1.3221421200212977</v>
       </c>
       <c r="C3" t="s">
         <v>11</v>
@@ -2052,7 +2645,7 @@
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -2061,7 +2654,7 @@
       </c>
       <c r="B4">
         <f>16.34*EXP(-0.0152*(Filtration_calculator!E2-28.6)^2 )*Filtration_calculator!D2^0.608</f>
-        <v>5.3728786251102285</v>
+        <v>2.5787422181471031</v>
       </c>
       <c r="C4" t="s">
         <v>41</v>
@@ -2079,7 +2672,7 @@
       </c>
       <c r="B5">
         <f>7.475*EXP(-0.00473*(Filtration_calculator!E2-29.1)^2 )*Filtration_calculator!D2^(0.75)</f>
-        <v>2.2322970162229376</v>
+        <v>0.90260245560773122</v>
       </c>
       <c r="C5" t="s">
         <v>45</v>
@@ -2097,7 +2690,7 @@
       </c>
       <c r="B6">
         <f>13.1*EXP(-0.0099*(Filtration_calculator!E2-28.3)^2)*Filtration_calculator!D2^0.617</f>
-        <v>4.6459352705033501</v>
+        <v>2.2057434063316479</v>
       </c>
       <c r="C6" t="s">
         <v>49</v>
@@ -2112,13 +2705,16 @@
       </c>
       <c r="B7">
         <f>4.16*EXP(-0.0181*(Filtration_calculator!E2-14.88)^2)*Filtration_calculator!D2^0.58</f>
-        <v>0.27217890510661769</v>
+        <v>0.13512537143423445</v>
       </c>
       <c r="C7" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D7" t="s">
-        <v>121</v>
+        <v>134</v>
+      </c>
+      <c r="E7" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -2127,13 +2723,13 @@
       </c>
       <c r="B8">
         <f>5.14*EXP(-0.00246*(Filtration_calculator!E2- 18.5)^2 )*Filtration_calculator!D2^0.7</f>
-        <v>1.6150476837206291</v>
+        <v>0.69366041661892741</v>
       </c>
       <c r="C8" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -2142,7 +2738,7 @@
       </c>
       <c r="B9">
         <f>2.54*EXP(-0.00411*(Filtration_calculator!E2-27.9)^2)*Filtration_calculator!D2^0.792</f>
-        <v>0.74479374844388146</v>
+        <v>0.28625840585825341</v>
       </c>
       <c r="C9" t="s">
         <v>42</v>
@@ -2168,16 +2764,13 @@
       </c>
       <c r="B11" s="2">
         <f>5.04*EXP(-0.0454*(Filtration_calculator!E2-29.3)^2)*Filtration_calculator!D2^0.764</f>
-        <v>0.68926001307004026</v>
+        <v>0.27402289304878119</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
@@ -2186,7 +2779,7 @@
       </c>
       <c r="B12">
         <f>(0.162+(0.072*1.131^Filtration_calculator!E2))*Filtration_calculator!D2^0.622</f>
-        <v>0.67622034421048982</v>
+        <v>0.31911584178111602</v>
       </c>
       <c r="C12" t="s">
         <v>44</v>
@@ -2204,10 +2797,10 @@
         <v>3.3183607362271923</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
@@ -2225,24 +2818,60 @@
       </c>
       <c r="B15">
         <f>2.454*(Filtration_calculator!D2)^0.492</f>
-        <v>1.1700905082900024</v>
+        <v>0.64601688502441423</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B16">
+        <f>18.3*EXP(-0.00889*(Filtration_calculator!E2- 26.8)^2 )*Filtration_calculator!D2^0.784</f>
+        <v>2.1198381241000814</v>
+      </c>
+      <c r="C16" t="s">
+        <v>177</v>
+      </c>
+      <c r="D16" t="s">
+        <v>176</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B17">
+        <f>12.3*EXP(-0.00889*(Filtration_calculator!E2- 26.8)^2 )*Filtration_calculator!D2^0.784</f>
+        <v>1.4248092309525136</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D17" t="s">
+        <v>176</v>
+      </c>
+      <c r="E17" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>47</v>
       </c>
@@ -2255,7 +2884,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{264C9648-2F22-B347-91A2-7EAEF7624D43}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.33203125" bestFit="1" customWidth="1"/>
@@ -2368,32 +2997,32 @@
     </row>
     <row r="10" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10" s="10" t="s">
         <v>78</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C12" t="str">
         <f>HYPERLINK("http://dx.doi.org/10.1007/s10152-013-0377-9","http://dx.doi.org/10.1007/s10152-013-0377-9")</f>
@@ -2402,10 +3031,10 @@
     </row>
     <row r="13" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C13" t="str">
         <f>HYPERLINK("http://dx.doi.org/10.3354/meps305147","http://dx.doi.org/10.3354/meps305147")</f>
@@ -2414,91 +3043,166 @@
     </row>
     <row r="14" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C14" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C16" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C17" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C18" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C19" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B20" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="C20" t="s">
         <v>122</v>
-      </c>
-      <c r="C20" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C21" t="s">
-        <v>126</v>
-      </c>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>132</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C22" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>146</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C23" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>163</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="C24" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>166</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>173</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="C26" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>175</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="C27" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="20" x14ac:dyDescent="0.2">
+      <c r="B28" s="13"/>
+    </row>
+    <row r="29" spans="1:3" ht="20" x14ac:dyDescent="0.2">
+      <c r="B29" s="12"/>
+    </row>
+    <row r="31" spans="1:3" ht="20" x14ac:dyDescent="0.2">
+      <c r="B31" s="13"/>
+    </row>
+    <row r="32" spans="1:3" ht="20" x14ac:dyDescent="0.2">
+      <c r="B32" s="13"/>
     </row>
   </sheetData>
   <hyperlinks>
